--- a/exported_docs/URT上升趋势策略功能模块列表.xlsx
+++ b/exported_docs/URT上升趋势策略功能模块列表.xlsx
@@ -11,14 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能模块完成列表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务链路完成情况" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待优化事项" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配套文档" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待跟踪事项" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配套文档" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'概览'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能模块完成列表'!$A$1:$F$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'概览'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'功能模块完成列表'!$A$1:$F$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'业务链路完成情况'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待优化事项'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'配套文档'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待优化事项'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待跟踪事项'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'配套文档'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,11 +513,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -561,12 +563,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>对照 GMS 完成清单结构梳理</t>
+          <t>对齐领导汇报版说明书 V1.2 与当前代码实现</t>
         </is>
       </c>
     </row>
@@ -578,12 +580,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>约 72%</t>
+          <t>约 93%</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>选股、预计算、信号追溯、Admin 回测主链路可用；交易链与港股未做</t>
+          <t>主链路已交付；结构出场/目标涨幅区间/任务完成时间等已落地</t>
         </is>
       </c>
     </row>
@@ -600,7 +602,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>硬筛通过后再按百分制得分过滤；不做左侧吸附</t>
+          <t>硬筛 + 结构/过热硬闸 + 得分≥最低分；不做左侧吸附</t>
         </is>
       </c>
     </row>
@@ -612,12 +614,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A股全市场 / 自选股 / 行业板块 / 概念板块 / 单股</t>
+          <t>A股 / 港股全市场 / 自选 / 行业概念 / 单股(仅A股)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>港股、ETF、观察股池尚未覆盖</t>
+          <t>ETF、GMS式版本观察股池未覆盖；日报与回测仅 A 股</t>
         </is>
       </c>
     </row>
@@ -629,96 +631,113 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>日 K 现算</t>
+          <t>日 K 现算 + 信号缓存</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>不依赖均值频率共振指标表；从 historical_quotes 计算 MA/量能/连阳</t>
+          <t>historical_quotes / historical_quotes_hk；可选读 urt_signal_trace</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>回测主口径</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>结构出场（支撑止损/阻力止盈）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>另可选命中率、纪律出场；缺省观察期 10 日；目标涨幅支持区间</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>主要待完善</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>选股页参数版本 UI、回测止损纪律、观察股/正式交易、推送、港股、审计</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>详见「待优化事项」表</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>统计项</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>量能硬筛/结构止损距离/冷却；ETF与版本观察股池待产品确认</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>详见「待优化事项」「待跟踪事项」页</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>统计项</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>功能项合计</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>34</v>
+      <c r="B11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>部分完成</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>4</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>未实现</t>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>一级模块数</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B15" s="4" t="n">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A1:C9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -729,15 +748,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -785,7 +804,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>收盘站上 MA20、连阳（4日≥3阳或5日≥4阳）、量能达阈值倍数</t>
+          <t>收盘站上 MA20、连阳（4日≥3阳或5日≥4阳）、量能达阈值倍数；可选中期阳线/多头/换手</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -798,7 +817,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>缺省量能倍数以参数版本为准</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -813,7 +836,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MA20/连阳/量能主分项；可选换手、量比加分</t>
+          <t>趋势/连阳/量能/结构位与盈亏比/换手等分项，封顶 100</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -828,7 +851,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>默认满分结构约 90 分</t>
+          <t>高分≠已贴近买点</t>
         </is>
       </c>
     </row>
@@ -840,12 +863,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>买点信号判定</t>
+          <t>结构硬闸</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>硬筛通过且得分≥最低分后输出买点</t>
+          <t>破位、贴/超阻力、上行空间不足、悬空离支撑等否决正式买点</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -860,7 +883,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>单股模式可跳过滤输出明细</t>
+          <t>RR 偏低仅提示不否决</t>
         </is>
       </c>
     </row>
@@ -872,12 +895,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>信号原因明细</t>
+          <t>过热硬闸</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>得分拆解、买点逻辑说明可追溯展示</t>
+          <t>近 10 日涨幅过大或相对 MA20 乖离过大否决买点；轻度过热提示扣分</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -900,44 +923,44 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>离场纪律函数</t>
+          <t>买点信号判定</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>价格止损、连跌离场、高点回撤止盈等规则实现</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+          <t>硬筛 + 结构/过热硬闸 + 得分≥最低分 → 正式买点</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>函数与配置已有，回测默认未调用</t>
+          <t>单股模式可跳过滤输出明细</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>数据基础</t>
+          <t>策略算法</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>日 K 行情依赖</t>
+          <t>信号原因明细</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>以 A 股 historical_quotes 为计算输入</t>
+          <t>得分拆解、结构位、RR、买点逻辑可追溯展示</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -952,24 +975,24 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>与 GMS 指标链路不同，属设计差异</t>
+          <t>支持导出 PDF</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>数据基础</t>
+          <t>策略算法</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>候选股票池</t>
+          <t>纪律出场规则</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>从股票基本信息过滤 ST、采集开关、代码位数等</t>
+          <t>价格止损、连跌（且浮亏达阈值）、高点回撤止盈</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -982,22 +1005,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>回测 exit_mode=risk_exit</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>数据基础</t>
+          <t>策略算法</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>板块前缀过滤</t>
+          <t>结构出场规则</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>创业板/科创/沪深主板/中小/北证等代码段过滤</t>
+          <t>支撑止损/阻力止盈；含保护、分批、百分比跟踪等</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1010,22 +1037,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>回测 exit_mode=structure_exit；当前验证重点</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>选股能力</t>
+          <t>数据基础</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>全 A 股筛选</t>
+          <t>日 K 行情依赖</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>全部 A 股范围扫描上升趋势信号</t>
+          <t>A 股 historical_quotes；港股 historical_quotes_hk</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1035,29 +1066,29 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>可设扫描上限与超时</t>
+          <t>与 GMS 指标链路不同，属设计差异</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>选股能力</t>
+          <t>数据基础</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>自选股筛选</t>
+          <t>候选股票池</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>按当前登录用户自选股池筛选</t>
+          <t>从股票基本信息过滤 ST、采集开关、代码位数等</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1070,22 +1101,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ST 为候选池硬剔除，无选股勾选开关</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>选股能力</t>
+          <t>数据基础</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>行业板块选股</t>
+          <t>板块前缀过滤</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>按行业板块成分股多选筛选</t>
+          <t>创业板/科创/沪深主板/中小/北证等代码段过滤</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1098,22 +1133,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>可多选并集</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>选股能力</t>
+          <t>数据基础</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>概念板块选股</t>
+          <t>全市场扫描占位</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>按概念板块成分股多选筛选</t>
+          <t>预计算写入 __URT_SCANNED__；全市场任务不认小池占位</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1123,10 +1162,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>避免股票池缓存冒充全市场</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1136,12 +1179,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>A 股板块分段</t>
+          <t>全 A 股筛选</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>主板/创业板/中小板/科创板/北证等分段</t>
+          <t>全部 A 股范围扫描上升趋势信号</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1151,10 +1194,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>可设扫描上限与超时</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1164,12 +1211,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>单股查询模式</t>
+          <t>自选股筛选</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>输入代码实时计算信号明细（可含未过筛结果）</t>
+          <t>按当前登录用户自选股池筛选</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1182,7 +1229,11 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>空自选=空结果</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1192,12 +1243,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>缓存优先选股</t>
+          <t>行业板块选股</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>无临时参数覆盖时优先读预计算信号表</t>
+          <t>按行业板块成分股多选筛选</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1207,7 +1258,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1220,12 +1271,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>得分明细展示</t>
+          <t>概念板块选股</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>选股页展开查看分项得分与买点逻辑</t>
+          <t>按概念板块成分股多选筛选</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1248,12 +1299,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>结果导出</t>
+          <t>A 股板块分段</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>筛选结果导出 CSV</t>
+          <t>主板/创业板/中小板/科创板/北证等分段</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1263,7 +1314,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1276,12 +1327,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>策略参数版本切换</t>
+          <t>单股查询模式</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>选股时可指定不同参数版本</t>
+          <t>输入代码实时计算信号明细（可含未过筛结果）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1291,12 +1342,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>API 支持 config_id，选股页尚未提供下拉</t>
+          <t>暂仅 6 位 A 股</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1359,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>港股/ETF 范围</t>
+          <t>缓存优先选股</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>港股或 ETF 市场范围筛选</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>无临时参数覆盖时优先读预计算信号表</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>计划后续</t>
-        </is>
-      </c>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1340,44 +1387,40 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>观察股池范围</t>
+          <t>得分明细展示</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>独立策略观察股池作为选股范围</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>选股页展开查看分项得分与买点逻辑</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>对齐 GMS 观察股能力</t>
-        </is>
-      </c>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>信号追溯</t>
+          <t>选股能力</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>历史信号查询</t>
+          <t>结果导出</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>单股按日期查看历史 URT 信号</t>
+          <t>筛选结果导出 CSV</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1395,17 +1438,17 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>信号追溯</t>
+          <t>选股能力</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>多版本切换</t>
+          <t>策略参数版本切换</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>历史页可切换参数版本查看</t>
+          <t>选股时可指定不同参数版本</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1418,22 +1461,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>前台 urt-config_id + config_id</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>信号追溯</t>
+          <t>选股能力</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>信号重算</t>
+          <t>港股范围</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>指定区间异步强制重算，支持进度查询</t>
+          <t>港股全市场选股 scope=hk</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1443,7 +1490,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1451,45 +1498,49 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>信号追溯</t>
+          <t>选股能力</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>计算明细页</t>
+          <t>ETF 范围</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>单股信号计算明细独立页面</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>独立 ETF 市场范围筛选</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>未实现</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>信号追溯</t>
+          <t>选股能力</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>追溯页单股回测</t>
+          <t>观察股池范围</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>在历史页发起单股回测</t>
+          <t>独立策略版本观察股池作为选股范围</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1504,24 +1555,24 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>GMS 已有对等能力</t>
+          <t>有用户侧交易观察，非版本池</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>信号预计算</t>
+          <t>信号追溯</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>定时全 A 预计算</t>
+          <t>历史信号查询</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>收盘后对全 A 股写入信号缓存</t>
+          <t>单股按日期查看历史 URT 信号</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1534,26 +1585,22 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>环境变量可开关与调度</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>信号预计算</t>
+          <t>信号追溯</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>手动触发预计算</t>
+          <t>多版本切换</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>管理端可手动跑预计算</t>
+          <t>历史页可切换参数版本查看</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1571,27 +1618,27 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>信号预计算</t>
+          <t>信号追溯</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>港股预计算</t>
+          <t>信号重算</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>港股日终信号预计算</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>指定区间异步强制重算，支持进度查询</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -1599,17 +1646,17 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>回测验证</t>
+          <t>信号追溯</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>目标命中率回测</t>
+          <t>计算明细页</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>次日开盘入场，观察期内达目标涨幅判定命中</t>
+          <t>单股信号计算明细独立页面；含结构/RR/买点建议</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1619,29 +1666,29 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>当前默认模式</t>
+          <t>可导出 PDF</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>回测验证</t>
+          <t>信号追溯</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>多范围回测</t>
+          <t>追溯页单股回测</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>支持全市场/自选等范围批量回测</t>
+          <t>在历史页发起单股回测</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1651,25 +1698,29 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/stock/urt-backtest</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>回测验证</t>
+          <t>信号预计算</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>任务管理</t>
+          <t>定时全 A 预计算</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>创建、查看、取消、重跑、删除回测任务</t>
+          <t>收盘后对全 A 股写入信号缓存</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1682,22 +1733,26 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>默认约 16:45</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>回测验证</t>
+          <t>信号预计算</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>报告与下载</t>
+          <t>手动触发预计算</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>报告列表、详情、CSV 导出</t>
+          <t>管理端可按交易日/市场/版本手动补算</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1707,61 +1762,61 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>暂无 xlsx</t>
+          <t>market=CN|HK</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>回测验证</t>
+          <t>信号预计算</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>止损纪律回测模式</t>
+          <t>港股预计算</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>持仓期按止损/连跌/回撤止盈出场</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+          <t>港股日终信号预计算</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>规则函数已实现，需接入 runner</t>
+          <t>默认约 17:20</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>策略配置</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>参数多版本管理</t>
+          <t>目标命中率回测</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>策略参数版本创建、编辑、默认版本</t>
+          <t>次日开盘入场；观察期内按目标涨幅区间判定命中</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1774,22 +1829,26 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>exit_mode=hit_rate；仅 A 股</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>策略配置</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>预计算开关</t>
+          <t>目标涨幅区间</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>按版本控制是否参与预计算</t>
+          <t>可设上下限；缺省 10%～10%；上下限不等则最大涨幅须落在区间内</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1802,22 +1861,26 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>冲破上限另计统计字段</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>策略配置</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>管理端试算预览</t>
+          <t>纪律出场回测</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>配置页可试算选股预览</t>
+          <t>持仓期按止损/连跌/回撤止盈出场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1827,141 +1890,157 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>exit_mode=risk_exit</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>策略配置</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>观察股版本分组</t>
+          <t>结构出场回测</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>按版本维护观察股池并绑定参数</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>支撑止损/阻力止盈；可附带命中率对照任务</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>GMS 有对等能力</t>
+          <t>exit_mode=structure_exit；当前主验证口径</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>交易执行</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>交易观察股</t>
+          <t>优先读缓存</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>从选股结果加入观察、列表管理、移除归档</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>全市场任务可读预计算缓存，避免实时扫五千股</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>建议全市场任务开启</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>交易执行</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>正式交易记录</t>
+          <t>多范围回测</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>从观察进入正式交易并记录仓位状态</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>支持全市场/自选/板块/单股/自定义等范围</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>市场仍仅 A 股</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>交易执行</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>选股页三子面板</t>
+          <t>任务管理</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>策略信号 / 交易观察 / 正式交易一体</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>创建、查看、取消、重跑、删除；列表展示完成时间</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>completed_at</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>用户端</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>选股页上升趋势标签</t>
+          <t>报告与下载</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>范围、参数、结果表、历史/明细入口</t>
+          <t>报告列表、详情、分桶统计；CSV / XLSX / PDF 导出</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1971,7 +2050,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -1979,17 +2058,17 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>用户端</t>
+          <t>回测验证</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>权限控制</t>
+          <t>命中率对照</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Tab/刷新/导出权限码控制可见性</t>
+          <t>结构/纪律任务可自动再跑一笔命中率对照</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2007,17 +2086,17 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>用户端</t>
+          <t>策略配置</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>信号追溯独立页</t>
+          <t>参数多版本管理</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>单股历史信号与重算</t>
+          <t>策略参数版本创建、编辑、默认/生效版本</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2030,32 +2109,36 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>urt_strategy_configs</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>用户端</t>
+          <t>策略配置</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>个股详情 URT 卡片</t>
+          <t>预计算开关</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>个股详情页展示 URT 指标与信号</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>按版本控制是否参与预计算</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2063,17 +2146,17 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>策略配置</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>URT 管理中心</t>
+          <t>管理端试算预览</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>策略参数、回测管理、报告与分析三 Tab</t>
+          <t>配置页可试算选股预览</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2083,7 +2166,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2091,27 +2174,27 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>策略配置</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>系统状态概览</t>
+          <t>偏离生效标记</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>运行中任务、失败统计等健康信息</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>回测选用非生效版本或覆盖最低分时标记偏离</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2119,17 +2202,17 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>策略配置</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>操作审计日志</t>
+          <t>观察股版本分组</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>参数修改、回测创建等操作留痕</t>
+          <t>按版本维护观察股池并绑定参数</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2142,96 +2225,100 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>管理端</t>
+          <t>交易执行</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>管理端选股结果</t>
+          <t>交易观察股</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>与网站端同源的选股结果查看</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>从选股结果加入观察、列表管理、移除归档</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>配置页有试算，无独立结果中心</t>
+          <t>urt_trade_observe*</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>推送报告</t>
+          <t>交易执行</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>URT 每日信号推送</t>
+          <t>正式交易记录</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>定时推送自选/当日 URT 信号日报</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>从观察进入正式交易并记录仓位状态</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>可复用现有推送管道</t>
+          <t>urt_formal_trade*</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>推送报告</t>
+          <t>交易执行</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>推送任务配置</t>
+          <t>选股页三子面板</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>管理端配置 URT 日报类型与收件人</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>策略信号 / 交易观察 / 正式交易一体</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -2239,17 +2326,17 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>部署运维</t>
+          <t>用户端</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>预计算调度配置</t>
+          <t>选股页上升趋势标签</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>环境变量开关与 cron 时间可配</t>
+          <t>范围、参数、结果表、历史/明细入口</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2262,42 +2349,354 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>含刷新筛选</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>权限控制</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Tab/刷新/导出权限码控制可见性</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>信号追溯独立页</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>单股历史信号与重算</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>用户端</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>个股详情 URT 卡片</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>个股详情页展示 URT 指标与信号入口</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>stock.js + urt-score-detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>URT 管理中心</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>策略参数、回测管理、报告与分析等页签</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>/urt-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>系统状态概览</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>运行中任务、失败统计等健康信息</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>GET /system/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>操作审计日志</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>参数修改、回测创建等操作留痕</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>operation_logs · urt_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>管理端选股结果</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>与网站端同源的独立选股结果中心</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>配置页有试算；体验增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>推送报告</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>URT 每日信号推送</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>定时推送自选 A 股 URT 信号日报（买点+连阳补充）</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>urt_daily；港股不进日报</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>推送报告</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>推送任务配置</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>管理端配置 URT 日报类型与收件人</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>建议约 17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>部署运维</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>预计算调度配置</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>环境变量开关与 cron 时间可配</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>部署运维</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>数据库迁移完整性</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>主业务表具备独立迁移脚本</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>部分完成</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>重算任务表已有；其余主表待补</t>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>add_urt_core_tables / trade_tables 等</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:F63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2312,7 +2711,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2347,7 +2746,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>日 K 采集 → 候选池过滤 → 现算 MA/量能/连阳</t>
+          <t>日 K 采集 → 候选池过滤 → 现算 MA/量能/连阳/结构</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2357,7 +2756,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>不依赖独立共振指标表</t>
+          <t>A/港行情表；不依赖独立共振指标表</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2768,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>硬筛 → 百分制得分 → 买点判定 → 明细拆解</t>
+          <t>硬筛 → 结构/过热硬闸 → 百分制得分 → 买点判定</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2379,7 +2778,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>离场纪律函数已写未接入回测</t>
+          <t>正式买点四条件同时满足</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2800,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>缺港股/ETF/观察股池；版本 UI 部分完成</t>
+          <t>含港股；缺 ETF/版本观察股池</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2812,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>定时全 A 预计算 → 缓存表 → 选股优先读库</t>
+          <t>定时 A/港预计算 → 缓存表 → 选股/回测优先读库</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2423,7 +2822,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>港股预计算未做</t>
+          <t>全市场占位与小池占位区分</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2834,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>区间查询 → 版本切换 → 异步重算 → 明细页</t>
+          <t>区间查询 → 版本切换 → 异步重算 → 明细页/PDF → 单股回测</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2443,11 +2842,7 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>缺追溯页单股回测</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -2457,7 +2852,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>任务创建 → 异步执行 → 报告/CSV</t>
+          <t>任务创建 → 命中率/纪律/结构出场 → 报告/CSV/XLSX/PDF</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2467,7 +2862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>默认命中率模式；止损模式待接</t>
+          <t>目标涨幅区间；仅 A 股；列表含完成时间</t>
         </is>
       </c>
     </row>
@@ -2479,17 +2874,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>选股信号 → 观察股 → 正式交易</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>选股信号 → 交易观察 → 正式交易</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>对齐 GMS 交易链为后续重点</t>
+          <t>非 GMS 式版本观察股池</t>
         </is>
       </c>
     </row>
@@ -2501,17 +2896,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>URT 日报 → 定时推送 → 休市跳过</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>未实现</t>
+          <t>urt_daily → 定时推送 → 休市跳过</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>可复用现有推送框架</t>
+          <t>仅自选 A 股；买点+连阳补充</t>
         </is>
       </c>
     </row>
@@ -2527,14 +2922,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2567,17 +2962,17 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>体验</t>
+          <t>策略</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>选股页参数版本下拉</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>提高量能硬筛阈值（试 3.5）</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2587,24 +2982,24 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>API 已支持 config_id，补齐前端版本选择</t>
+          <t>样本中 &lt;3.5 倍占比高、均盈偏低</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>回测</t>
+          <t>策略</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>接入止损/连跌/回撤离场模式</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+          <t>结构止损最小距离（3%～4% 否则回退）</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2614,51 +3009,51 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>与命中率模式并存，任务参数可选</t>
+          <t>近支撑止损偏密，易被洗</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>交易</t>
+          <t>策略</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>交易观察股与正式交易台账</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>止损后再进场冷却</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>垂直切片对齐 GMS，独立 URT 表与路由</t>
+          <t>结构出场同票易回补；建议冷却至观察期末或≥5 日</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>运营</t>
+          <t>策略</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>收盘微信/邮件 URT 日报</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>峰值回撤参数微调</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2668,120 +3063,309 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>新增 urt_daily 报告类型</t>
+          <t>已达 +10% 余仓可略放宽回撤</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>市场</t>
+          <t>策略</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>港股选股与预计算</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>连跌叠加跌破 MA20</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>扩展数据加载与定时任务</t>
+          <t>纪律出场已条件化浮亏，尚未接均线</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>运维</t>
+          <t>回测</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Admin 审计日志与系统状态</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>得分因子明细分桶完善</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>待开发</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>对齐 GMS 管理端运维能力</t>
+          <t>缺 score_detail 时因子表不完整</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>体验</t>
+          <t>市场</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>个股详情页 URT 卡片</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>计划中</t>
+          <t>ETF 独立选股池</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>详情页展示当日信号与得分</t>
+          <t>当前未纳入 URT</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>市场</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>主表独立 migrations 补齐</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+          <t>GMS 式版本观察股池</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>与现有交易观察关系待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>港股回测</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>选股/预计算已支持；回测仅 A 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>港股单股明细 / 日报推送</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>单股以 6 位 A 股为主；日报仅自选 A 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ST 剔除可选开关</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>待产品确认</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>低</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>configs/trace/backtest 正式迁移脚本</t>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>当前候选池硬剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>管理端参数版本对比/克隆</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>体验增强</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>已有 CRUD 与默认生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>管理端独立选股结果中心</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>体验增强</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>配置页可试算；网站端选股已可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>结构出场全路径/目标涨幅区间/任务完成时间</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>以领导汇报版与回测说明为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>选股页参数版本 / 交易观察 / urt_daily / 港股预计算</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>主链路归档</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2792,10 +3376,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪项</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>责任侧重</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>结构出场主样本复验</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>策略 / 研发</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>全市场+结构出场+观察期10+生效版本+读缓存；对照量能3.5/止损距离/冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>全市场缓存覆盖正确性</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>研发 / 运维</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>小池占位不得冒充全市场；信号量级宜至千级而非数十/三百级异常偏低需排查参数与缓存</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>参数版本与预计算一致性</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>改参设生效后须补预计算，避免选股/回测读旧缓存</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>自选股结构出场小样本</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>用观察期10与结构保护规则重跑验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>命中率模式使用边界</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>业务 / 管理</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>命中率仅统计对照，不作实盘持有建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>产品缺口确认闭环</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ETF/版本池/港股扩展形成做或不做结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>回测报告归档口径</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>关缓存或信号过少任务不宜作主结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>与 GMS 能力边界</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>产品 / 研发</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>对齐能力面，不引入左侧轨/MFR/双模块评分</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2814,84 +3617,84 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>URT 策略实现设计</t>
+          <t>URT 上升趋势策略说明书（领导汇报版）</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>策略定义、得分规则、API、权限、二期预计算与回测</t>
+          <t>策略定义、业务规则、交付清单、界面入口、待优化与待跟踪（管理层）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URT 策略交易回测说明</t>
+          <t>URT 上升趋势业务简化版</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>命中率回测买卖与观察期规则</t>
+          <t>业务口径（以代码为准）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>URT 与 GMS 功能对比及技术方案</t>
+          <t>URT 策略交易回测说明</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>模块对照、缺口与落地路径（本文配套）</t>
+          <t>买卖规则、出场模式、目标涨幅区间、导出字段</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>URT 上升趋势策略落地计划</t>
+          <t>URT 策略回测优化方案</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>一期/二期范围与后续项</t>
+          <t>主样本结论与策略优化待办</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GMS 策略功能模块完成列表</t>
+          <t>URT 与 GMS 功能对比及技术方案</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>对照基准（Excel）</t>
+          <t>模块对照、已落地/待办技术方案</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GMS 策略实现设计</t>
+          <t>URT 策略实现设计</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GMS 架构参考</t>
+          <t>策略定义、得分规则、API、权限、预计算与回测</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GMS 回测管理中心手册</t>
+          <t>GMS 策略功能模块完成列表</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>管理端回测交互参考</t>
+          <t>对照基准（Excel）</t>
         </is>
       </c>
     </row>
